--- a/data/CReDEs/jy/jy_xbs.xlsx
+++ b/data/CReDEs/jy/jy_xbs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\九院-标准化\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\九院-标准化\CRedes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C785F78-54D6-4586-AC26-51E50F0D5BC0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDB8E33-DFD4-469D-888A-09DC5625A9F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11805" xr2:uid="{7B849D71-1F07-4AB1-8B7D-CC4C81F0C1C7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
   <si>
     <t>标签名称</t>
   </si>
@@ -201,6 +201,13 @@
   </si>
   <si>
     <t>1=口腔扁平苔藓， 2=口腔黏膜下纤维性变， 3=盘状红斑狼疮， 4=上皮过角化， 5=先天性角化不良， 6=梅毒， 7=艾滋病， 8=白斑， 9=红斑</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -645,7 +652,9 @@
       <c r="E3" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -663,7 +672,9 @@
       <c r="E4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
@@ -681,7 +692,9 @@
       <c r="E5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -699,7 +712,9 @@
       <c r="E6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -737,7 +752,9 @@
       <c r="E8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
@@ -755,7 +772,9 @@
       <c r="E9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -773,7 +792,9 @@
       <c r="E10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
@@ -811,7 +832,9 @@
       <c r="E12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
@@ -829,7 +852,9 @@
       <c r="E13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -879,5 +904,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>